--- a/data/speciesTauBinom.xlsx
+++ b/data/speciesTauBinom.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12884</v>
+        <v>12886</v>
       </c>
       <c r="C2" t="n">
-        <v>3007</v>
+        <v>3232</v>
       </c>
       <c r="D2" t="n">
-        <v>15891</v>
+        <v>16118</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C3" t="n">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="D3" t="n">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="E3" t="n">
-        <v>2.777689767000973e-25</v>
+        <v>3.65519529372356e-12</v>
       </c>
     </row>
     <row r="4">
@@ -486,13 +486,13 @@
         <v>631</v>
       </c>
       <c r="C4" t="n">
-        <v>158</v>
+        <v>774</v>
       </c>
       <c r="D4" t="n">
-        <v>789</v>
+        <v>1405</v>
       </c>
       <c r="E4" t="n">
-        <v>1.122532949142959e-67</v>
+        <v>0.0001498234607155243</v>
       </c>
     </row>
     <row r="5">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>857</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>331</v>
+        <v>3115</v>
       </c>
       <c r="D5" t="n">
-        <v>1189</v>
+        <v>4008</v>
       </c>
       <c r="E5" t="n">
-        <v>3.584733907524416e-54</v>
+        <v>3.856226737966762e-293</v>
       </c>
     </row>
   </sheetData>
